--- a/c/Complexity_Chart.xlsx
+++ b/c/Complexity_Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\uca_2026\c\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18A042B-892B-4C50-ADD1-53889CC5819A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748AAF4B-ECCE-4400-84C7-F8EF31A53C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,7 +445,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="1"/>
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
@@ -1142,10 +1142,10 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3829050" cy="2714625"/>
+    <xdr:ext cx="3832860" cy="2693670"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="1830814073" name="Chart 1" title="Chart">
